--- a/outputs/daily/hr_rankings_2026-08-10.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-10.xlsx
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>26.4</v>
+        <v>24.9</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Last 7 games: 8/28, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -9567,27 +9567,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>701807</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:15:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9597,17 +9597,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>693821</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9630,26 +9630,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>48.3</v>
+        <v>34.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>32.4</v>
+        <v>40.9</v>
       </c>
       <c r="R34" t="n">
-        <v>22.6</v>
+        <v>30.9</v>
       </c>
       <c r="S34" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T34" t="n">
         <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>72.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 20.5 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -9735,104 +9735,104 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>100.5329</t>
+          <t>100.0859</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.4627</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.2053</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.3309</t>
+          <t>0.343</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>8.46</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.3436</t>
+          <t>0.4067</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1554</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr"/>
       <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9843,27 +9843,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>701807</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-10T23:15:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9873,17 +9873,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>693821</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9906,20 +9906,20 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>34.8</v>
+        <v>48.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>40.9</v>
+        <v>32.4</v>
       </c>
       <c r="R35" t="n">
-        <v>30.9</v>
+        <v>22.6</v>
       </c>
       <c r="S35" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T35" t="n">
         <v>80</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 20.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -10011,104 +10011,104 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>100.0859</t>
+          <t>100.5329</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>0.4627</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.2053</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>0.3309</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>8.46</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.4067</t>
+          <t>0.3436</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1554</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10444,7 +10444,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>50</v>
       </c>
       <c r="U37" t="n">
-        <v>75.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -15688,7 +15688,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>50</v>
       </c>
       <c r="U56" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
@@ -20689,7 +20689,7 @@
         <v>50</v>
       </c>
       <c r="U74" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -20760,7 +20760,7 @@
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
@@ -23643,27 +23643,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-11T01:45:00Z</t>
+          <t>2026-08-10T23:15:00Z</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -23673,17 +23673,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Christian Scott</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>681035</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -23706,26 +23706,26 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>40.5</v>
+        <v>51.8</v>
       </c>
       <c r="Q85" t="n">
-        <v>18.6</v>
+        <v>24.6</v>
       </c>
       <c r="R85" t="n">
-        <v>19.3</v>
+        <v>30.9</v>
       </c>
       <c r="S85" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T85" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U85" t="n">
-        <v>56.2</v>
+        <v>64.3</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
@@ -23764,7 +23764,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr"/>
@@ -23781,12 +23781,12 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
@@ -23801,7 +23801,7 @@
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.8% barrel, 1.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
@@ -23811,104 +23811,104 @@
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>46.28</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>100.7812</t>
+          <t>102.8655</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.4118</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1907</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3069</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>75.83</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>55.07</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>39.66</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>30.94</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>0.1696</t>
+          <t>0.1526</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>87.08</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD85" t="inlineStr">
         <is>
-          <t>0.3709</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
-          <t>0.1229</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="BF85" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BG85" t="inlineStr"/>
       <c r="BH85" t="inlineStr"/>
       <c r="BI85" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ85" t="inlineStr"/>
@@ -23919,27 +23919,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-10T23:15:00Z</t>
+          <t>2026-08-11T01:45:00Z</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -23949,17 +23949,17 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Christian Scott</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>681035</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -23982,26 +23982,26 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>51.8</v>
+        <v>40.5</v>
       </c>
       <c r="Q86" t="n">
-        <v>24.6</v>
+        <v>18.6</v>
       </c>
       <c r="R86" t="n">
-        <v>30.9</v>
+        <v>19.3</v>
       </c>
       <c r="S86" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T86" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U86" t="n">
-        <v>64.3</v>
+        <v>54.4</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -24040,7 +24040,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr"/>
@@ -24057,12 +24057,12 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -24077,7 +24077,7 @@
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.8% barrel, 1.9 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -24087,104 +24087,104 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>46.28</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>102.8655</t>
+          <t>100.7812</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.4118</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.1907</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.3069</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>75.83</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>55.07</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>39.66</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>0.1526</t>
+          <t>0.1696</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.08</t>
         </is>
       </c>
       <c r="BD86" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.3709</t>
         </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.1229</t>
         </is>
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="BG86" t="inlineStr"/>
       <c r="BH86" t="inlineStr"/>
       <c r="BI86" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ86" t="inlineStr"/>
@@ -30868,7 +30868,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>80</v>
       </c>
       <c r="U111" t="n">
-        <v>18</v>
+        <v>16.6</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -30972,7 +30972,7 @@
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr">
@@ -32281,7 +32281,7 @@
         <v>50</v>
       </c>
       <c r="U116" t="n">
-        <v>25.8</v>
+        <v>24</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -32352,7 +32352,7 @@
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 7/25, 0 HR</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
@@ -35102,7 +35102,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
@@ -35112,7 +35112,7 @@
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/27, 1 HR</t>
+          <t>Last 7 games: 3/28, 1 HR</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
@@ -36421,7 +36421,7 @@
         <v>80</v>
       </c>
       <c r="U131" t="n">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
@@ -36492,7 +36492,7 @@
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 1 HR</t>
+          <t>Last 7 games: 3/24, 1 HR</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
@@ -37492,7 +37492,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>75</v>
       </c>
       <c r="U135" t="n">
-        <v>16.6</v>
+        <v>20.9</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -37581,12 +37581,12 @@
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
@@ -37596,7 +37596,7 @@
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
@@ -38872,7 +38872,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>50</v>
       </c>
       <c r="U140" t="n">
-        <v>61.4</v>
+        <v>59.3</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
@@ -38976,7 +38976,7 @@
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Contact streak: 11/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL140" t="inlineStr">
@@ -40252,7 +40252,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>50</v>
       </c>
       <c r="U145" t="n">
-        <v>17.7</v>
+        <v>16.1</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
@@ -40356,7 +40356,7 @@
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
@@ -40561,7 +40561,7 @@
         <v>50</v>
       </c>
       <c r="U146" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
@@ -40632,7 +40632,7 @@
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
@@ -43840,7 +43840,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>50</v>
       </c>
       <c r="U158" t="n">
-        <v>59</v>
+        <v>56.6</v>
       </c>
       <c r="V158" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
@@ -43944,7 +43944,7 @@
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Contact streak: 9/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL158" t="inlineStr">
@@ -44944,7 +44944,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>50</v>
       </c>
       <c r="U162" t="n">
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
       <c r="V162" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
@@ -45048,7 +45048,7 @@
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
@@ -46324,7 +46324,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>80</v>
       </c>
       <c r="U167" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="V167" t="inlineStr">
         <is>
@@ -46418,7 +46418,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ167" t="inlineStr">
@@ -46428,7 +46428,7 @@
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>Contact streak: 6/14 over last 7 games</t>
+          <t>Contact streak: 6/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL167" t="inlineStr">
@@ -50238,7 +50238,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>26.4</v>
+        <v>24.9</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -50342,7 +50342,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Last 7 games: 8/28, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
